--- a/site/public/admin/event2027/files/snu2027_vendor_response_form.xlsx
+++ b/site/public/admin/event2027/files/snu2027_vendor_response_form.xlsx
@@ -597,7 +597,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>서울대학교 경영대학 동창회 창립총회 행사기획팀  |  2027. 4. 16.(금) 18:00–21:00 · 그랜드 하얏트 서울 Grand Ballroom · 약 700명(600~800명)</t>
+          <t>서울대학교 경영대학 총동문회 창립총회 행사기획팀  |  2027. 4. 16.(금) 18:00–21:00 · 그랜드 하얏트 서울 Grand Ballroom · 약 700명(600~800명)</t>
         </is>
       </c>
     </row>

--- a/site/public/admin/event2027/files/snu2027_vendor_response_form.xlsx
+++ b/site/public/admin/event2027/files/snu2027_vendor_response_form.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>호텔 식음료를 제외한 행사 총괄 기획·제작·운영 범위 약 1억 2,000만~1억 3,000만원 (대행 수수료 총액이 아님). 부가세 포함 총액과 별도 금액을 모두 기재.</t>
+          <t>호텔 식음료를 제외한 행사 총괄 기획·제작·운영 범위 부가세 포함 약 1억 2,000만~1억 3,000만원 (대행 수수료 총액이 아님). 견적은 공급가액과 부가세를 구분해 기재.</t>
         </is>
       </c>
     </row>
